--- a/data/projects/drum-mass/REPORT.xlsx
+++ b/data/projects/drum-mass/REPORT.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-19</t>
         </is>
       </c>
     </row>
@@ -753,17 +753,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>검증완료</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>검증완료</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-08</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-19</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-26</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-12-05</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-08</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
